--- a/artfynd/A 22621-2023 artfynd.xlsx
+++ b/artfynd/A 22621-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22621-2023 artfynd.xlsx
+++ b/artfynd/A 22621-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105311721</v>
+        <v>105315004</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573320.1201639269</v>
+        <v>573384</v>
       </c>
       <c r="R2" t="n">
-        <v>6904703.62520273</v>
+        <v>6904662</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105311718</v>
+        <v>105315005</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573357.8128523328</v>
+        <v>573373</v>
       </c>
       <c r="R3" t="n">
-        <v>6904665.315866644</v>
+        <v>6904763</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105311724</v>
+        <v>105315003</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1205</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573181.5034395228</v>
+        <v>573301</v>
       </c>
       <c r="R4" t="n">
-        <v>6904706.193423533</v>
+        <v>6904654</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,21 +947,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,11 +960,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>På sälg</t>
-        </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1034,16 +984,11 @@
         <v>105311723</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1071,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573292.0287313769</v>
+        <v>573292</v>
       </c>
       <c r="R5" t="n">
-        <v>6904729.565945758</v>
+        <v>6904730</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,19 +1049,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105311725</v>
+        <v>105311729</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573197.6218119481</v>
+        <v>573384</v>
       </c>
       <c r="R6" t="n">
-        <v>6904694.432307635</v>
+        <v>6904683</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,21 +1151,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1247,7 +1167,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -1270,15 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105311728</v>
+        <v>105311716</v>
       </c>
       <c r="B7" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573398.6352576913</v>
+        <v>573456</v>
       </c>
       <c r="R7" t="n">
-        <v>6904675.990450514</v>
+        <v>6904741</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1343,19 +1258,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1392,37 +1297,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105311720</v>
+        <v>105311717</v>
       </c>
       <c r="B8" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573332.6813011344</v>
+        <v>573460</v>
       </c>
       <c r="R8" t="n">
-        <v>6904683.867499568</v>
+        <v>6904729</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1465,19 +1365,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,37 +1399,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105311729</v>
+        <v>105311718</v>
       </c>
       <c r="B9" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1549,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573383.5605671678</v>
+        <v>573358</v>
       </c>
       <c r="R9" t="n">
-        <v>6904682.649061328</v>
+        <v>6904665</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1582,21 +1467,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1605,11 +1480,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -1631,15 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105311730</v>
+        <v>105311722</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573400.2869103408</v>
+        <v>573318</v>
       </c>
       <c r="R10" t="n">
-        <v>6904685.809568285</v>
+        <v>6904705</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,21 +1569,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1727,11 +1582,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -1753,37 +1603,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105311731</v>
+        <v>105311724</v>
       </c>
       <c r="B11" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1793,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573399.3135911142</v>
+        <v>573182</v>
       </c>
       <c r="R11" t="n">
-        <v>6904687.651737954</v>
+        <v>6904706</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1826,21 +1671,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1849,6 +1684,11 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -1870,15 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105311716</v>
+        <v>105311725</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573456.0067090489</v>
+        <v>573198</v>
       </c>
       <c r="R12" t="n">
-        <v>6904740.600562851</v>
+        <v>6904694</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1943,21 +1778,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1969,7 +1794,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -1992,15 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105311717</v>
+        <v>105311726</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573460.0018647261</v>
+        <v>573202</v>
       </c>
       <c r="R13" t="n">
-        <v>6904728.575761078</v>
+        <v>6904692</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2065,21 +1885,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2088,6 +1898,11 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>På sälglåga</t>
+        </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -2109,37 +1924,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105311727</v>
+        <v>105311728</v>
       </c>
       <c r="B14" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2149,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573392.6646767803</v>
+        <v>573399</v>
       </c>
       <c r="R14" t="n">
-        <v>6904671.667289293</v>
+        <v>6904676</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2182,19 +1992,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2231,37 +2031,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>105315003</v>
+        <v>105311730</v>
       </c>
       <c r="B15" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1205</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2271,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573301.1454834709</v>
+        <v>573400</v>
       </c>
       <c r="R15" t="n">
-        <v>6904653.830185424</v>
+        <v>6904686</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2304,21 +2099,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2327,6 +2112,11 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -2351,12 +2141,7 @@
         <v>105311732</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2388,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573397.4890167546</v>
+        <v>573397</v>
       </c>
       <c r="R16" t="n">
-        <v>6904685.748447534</v>
+        <v>6904686</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2421,19 +2206,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,37 +2245,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>105311726</v>
+        <v>105311731</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2510,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573202.3356777227</v>
+        <v>573399</v>
       </c>
       <c r="R17" t="n">
-        <v>6904692.205725545</v>
+        <v>6904688</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2543,21 +2313,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2566,11 +2326,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>På sälglåga</t>
-        </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -2592,37 +2347,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>105311722</v>
+        <v>105311719</v>
       </c>
       <c r="B18" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2632,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573318.2244293451</v>
+        <v>573344</v>
       </c>
       <c r="R18" t="n">
-        <v>6904704.981399897</v>
+        <v>6904679</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2665,21 +2415,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2688,6 +2428,11 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>På rönnhögstubbe</t>
+        </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -2709,37 +2454,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>105315004</v>
+        <v>105311721</v>
       </c>
       <c r="B19" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2749,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573384.0182100661</v>
+        <v>573320</v>
       </c>
       <c r="R19" t="n">
-        <v>6904661.69535699</v>
+        <v>6904704</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2782,19 +2522,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2826,15 +2556,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>105311719</v>
+        <v>105311727</v>
       </c>
       <c r="B20" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2842,21 +2567,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2866,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>573343.5183713102</v>
+        <v>573393</v>
       </c>
       <c r="R20" t="n">
-        <v>6904678.979599514</v>
+        <v>6904672</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2899,21 +2624,11 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2925,7 +2640,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>På rönnhögstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -2948,37 +2663,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>105315005</v>
+        <v>105311720</v>
       </c>
       <c r="B21" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2988,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>573373.3975478985</v>
+        <v>573333</v>
       </c>
       <c r="R21" t="n">
-        <v>6904763.485515089</v>
+        <v>6904684</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3021,19 +2731,9 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 22621-2023 artfynd.xlsx
+++ b/artfynd/A 22621-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315004</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315005</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311723</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311729</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311716</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311717</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311718</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311722</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1707,6 +1757,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311724</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311725</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1921,6 +1981,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311726</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2028,6 +2093,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311728</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2135,6 +2205,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311730</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2242,6 +2317,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311732</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311731</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2451,6 +2536,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311719</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2553,6 +2643,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311721</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2660,6 +2755,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311727</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2762,8 +2862,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105311720</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>